--- a/static/planilhas/dados_vinculo.xlsx
+++ b/static/planilhas/dados_vinculo.xlsx
@@ -413,197 +413,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Funcionário</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Vínculo</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Líquido</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>ANTONIO DE SOUZA SANTOS</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Celetista</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>2.649,62</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>JOAO OLIVEIRA DOS SANTOS</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Celetista</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>1.758,40</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>JOSE ROBERTO DA SILVA HENRIQUE</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Celetista</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>1.017,75</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>MARIA DAS GRACAS LOPES DE OLIVEIRA</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Celetista</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>202,83</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Diniz da Silva Angelo</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Celetista</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>2.241,30</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Luiz Antonio Borgaco</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Celetista</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>321,31</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>GABRIEL DA SOLEDADE SANTOS</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Celetista</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>1.506,93</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>GEORGE WASHINGTON OLIVEIRA SANTOS</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Celetista</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>2.124,99</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>LUAN VITOR DA SILVA DE JESUS</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Celetista</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>1.352,36</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>REGINALDO DE SOUZA</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Celetista</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>0,00</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>